--- a/output7/【河洛文讀注音-注音二式】《蒹葭》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《蒹葭》.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F90E748-9137-4830-AD94-16E315AF6FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D64329D-69AE-434A-A2FC-08D8100A6C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
-    <sheet name="env" sheetId="8" r:id="rId1"/>
-    <sheet name="標音字庫" sheetId="129" r:id="rId2"/>
-    <sheet name="缺字表" sheetId="128" r:id="rId3"/>
-    <sheet name="漢字注音" sheetId="9" r:id="rId4"/>
-    <sheet name="缺字表 (範例)" sheetId="110" r:id="rId5"/>
-    <sheet name="標音字庫 (範例)" sheetId="121" r:id="rId6"/>
-    <sheet name="漢字注音 (範例)" sheetId="120" r:id="rId7"/>
+    <sheet name="人工標音字庫" sheetId="130" r:id="rId1"/>
+    <sheet name="env" sheetId="8" r:id="rId2"/>
+    <sheet name="標音字庫" sheetId="129" r:id="rId3"/>
+    <sheet name="缺字表" sheetId="128" r:id="rId4"/>
+    <sheet name="漢字注音" sheetId="9" r:id="rId5"/>
+    <sheet name="缺字表 (範例)" sheetId="110" r:id="rId6"/>
+    <sheet name="標音字庫 (範例)" sheetId="121" r:id="rId7"/>
+    <sheet name="漢字注音 (範例)" sheetId="120" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="FILE_NAME">env!$C$5</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2671" uniqueCount="1283">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4350,6 +4351,25 @@
   <si>
     <t>https://i.epochtimes.com/assets/uploads/2018/09/346078.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【河洛文讀注音-注音二式】《蒹葭》.xlsx</t>
   </si>
 </sst>
 </file>
@@ -6668,6 +6688,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E264A08-8CD3-496D-B198-97EBDC538CE8}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE3F7CD-091D-4D80-9C13-B10BCE8AB79E}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -6715,7 +6760,9 @@
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="4" t="s">
@@ -6870,23 +6917,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B97B597-A349-4AA6-ABCA-CB8836843986}">
   <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1278</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1279</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1280</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7419,31 +7466,6 @@
       </c>
       <c r="D39" t="s">
         <v>1260</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D242A72C-1CAB-47F9-B18C-0B62E885A3F9}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -7453,6 +7475,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D242A72C-1CAB-47F9-B18C-0B62E885A3F9}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B653E275-5A31-466A-99DB-0BBFEE8A78C6}">
   <dimension ref="A1:V2002"/>
   <sheetFormatPr defaultRowHeight="39"/>
@@ -47962,7 +48009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2180A89-0265-4346-97D5-5D16606F5B0F}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -48126,7 +48173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD15F3BA-C880-4104-B992-B0FF90EEBE97}">
   <dimension ref="A1:E238"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -52184,7 +52231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C93001D-D880-46B9-9D80-7A0F5AA84ACC}">
   <dimension ref="A1:V241"/>
   <sheetFormatPr defaultRowHeight="39"/>
